--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6165-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6165-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17691831-EC71-49EB-8ED2-15B3C39DA286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1BF5DDA-9ED2-4975-A17D-9D1CAEE7564A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8D524ABA-DF80-4AB3-8F87-877EF2A5F44B}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{35F6D436-3EDB-49BA-9F62-1877E227564D}"/>
   </bookViews>
   <sheets>
     <sheet name="6165-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1535,27 +1535,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB2D9208-0BD6-4194-BA7B-480600FCE0CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491FE84E-0C95-4CDB-908F-E5C2B361728D}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1589,7 +1588,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1625,7 +1624,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1677,7 +1676,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1745,7 +1744,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1817,7 +1816,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1889,7 +1888,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1961,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2033,7 +2032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2105,7 +2104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2177,7 +2176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2249,7 +2248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2321,7 +2320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2393,7 +2392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2465,7 +2464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2537,7 +2536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2609,7 +2608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2681,7 +2680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2753,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2825,7 +2824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2897,7 +2896,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -2969,7 +2968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3041,7 +3040,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="41">
         <v>2006</v>
       </c>
@@ -3113,7 +3112,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="43"/>
       <c r="B24" s="44"/>
       <c r="C24" s="18" t="s">
@@ -3141,7 +3140,7 @@
       <c r="W24" s="50"/>
       <c r="X24" s="46"/>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="51">
         <v>2005</v>
       </c>
@@ -3213,7 +3212,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="53"/>
       <c r="B26" s="54"/>
       <c r="C26" s="20" t="s">
@@ -3241,7 +3240,7 @@
       <c r="W26" s="60"/>
       <c r="X26" s="56"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2004</v>
       </c>
@@ -3313,7 +3312,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="43"/>
       <c r="B28" s="44"/>
       <c r="C28" s="18" t="s">
@@ -3341,7 +3340,7 @@
       <c r="W28" s="50"/>
       <c r="X28" s="46"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="51">
         <v>2003</v>
       </c>
@@ -3413,7 +3412,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="53"/>
       <c r="B30" s="54"/>
       <c r="C30" s="20" t="s">
@@ -3441,7 +3440,7 @@
       <c r="W30" s="60"/>
       <c r="X30" s="56"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2002</v>
       </c>
@@ -3513,7 +3512,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="51">
         <v>2001</v>
       </c>
@@ -3585,7 +3584,7 @@
         <v>7.43</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="53"/>
       <c r="B33" s="54"/>
       <c r="C33" s="20" t="s">
@@ -3613,7 +3612,7 @@
       <c r="W33" s="60"/>
       <c r="X33" s="56"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="41">
         <v>2000</v>
       </c>
@@ -3685,7 +3684,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="43"/>
       <c r="B35" s="44"/>
       <c r="C35" s="18" t="s">
@@ -3713,7 +3712,7 @@
       <c r="W35" s="50"/>
       <c r="X35" s="46"/>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>1999</v>
       </c>
@@ -3785,7 +3784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1998</v>
       </c>
@@ -3857,7 +3856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39" t="s">
         <v>47</v>
       </c>
